--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:15:24+00:00</t>
+    <t>2026-09-02T14:33:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:35+00:00</t>
+    <t>2026-09-02T15:03:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>MII PR MolGen Molekulare Biomarker</t>
+    <t>MII PR MolGen Molekularer Biomarker</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:03:15+00:00</t>
+    <t>2026-09-03T06:40:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:40:42+00:00</t>
+    <t>2026-09-03T06:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:57:15+00:00</t>
+    <t>2026-09-03T07:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:38:27+00:00</t>
+    <t>2026-09-03T07:56:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:56:27+00:00</t>
+    <t>2026-09-03T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T08:11:50+00:00</t>
+    <t>2026-09-03T08:25:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
